--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_383_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_383_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>43:47</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -1531,16 +1531,16 @@
         <v>23</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>60:30</t>
+          <t>30:31</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>44:43</t>
+          <t>24:44</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50:13</t>
+          <t>30:13</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>35:16</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2315,10 +2315,10 @@
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>05:07</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>30:27</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>3</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>58:28</t>
+          <t>28:28</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>61:25</t>
+          <t>31:25</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -3435,16 +3435,16 @@
         <v>99</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>25</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>59:43</t>
+          <t>29:43</t>
         </is>
       </c>
       <c r="AN33" t="n">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
         <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AN34" t="n">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>32:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>4</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>45:26</t>
+          <t>25:26</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>27:54</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>74:05</t>
+          <t>34:06</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -5860,10 +5860,10 @@
         <v>19</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>58:04</t>
+          <t>28:04</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>30:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -6392,16 +6392,16 @@
         <v>80</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>21</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_383_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_383_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -1531,16 +1531,16 @@
         <v>23</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -1923,10 +1923,10 @@
         <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>3</v>
@@ -3435,16 +3435,16 @@
         <v>99</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X28" t="n">
         <v>25</v>
@@ -4096,7 +4096,7 @@
         <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>4</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>19</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         <v>80</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>21</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_383_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_383_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" t="n">
         <v>21</v>
-      </c>
-      <c r="O3" t="n">
-        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2915,14 +2915,14 @@
         <v>2</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3447,14 +3447,14 @@
         <v>8</v>
       </c>
       <c r="X28" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y43" t="n">
         <v>6</v>
       </c>
-      <c r="Y43" t="n">
-        <v>7</v>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6404,14 +6404,14 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y46" t="n">
         <v>21</v>
       </c>
-      <c r="Y46" t="n">
-        <v>26</v>
-      </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="AA46" t="n">
